--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129229355</v>
       </c>
       <c r="B2" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129229341</v>
       </c>
       <c r="B3" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129229351</v>
       </c>
       <c r="B5" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129229354</v>
       </c>
       <c r="B6" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129229342</v>
       </c>
       <c r="B7" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229358</v>
+        <v>129229337</v>
       </c>
       <c r="B8" t="n">
-        <v>75155</v>
+        <v>86810</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R8" t="n">
-        <v>6410544</v>
+        <v>6410736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129229337</v>
+        <v>129229358</v>
       </c>
       <c r="B9" t="n">
-        <v>86806</v>
+        <v>75157</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3712</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R9" t="n">
-        <v>6410736</v>
+        <v>6410544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129229335</v>
       </c>
       <c r="B11" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129229353</v>
       </c>
       <c r="B12" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229344</v>
+        <v>129229347</v>
       </c>
       <c r="B13" t="n">
-        <v>75155</v>
+        <v>86948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723497</v>
+        <v>723429</v>
       </c>
       <c r="R13" t="n">
-        <v>6410619</v>
+        <v>6410682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129229329</v>
+        <v>129229348</v>
       </c>
       <c r="B14" t="n">
-        <v>87004</v>
+        <v>86810</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723312</v>
+        <v>723376</v>
       </c>
       <c r="R14" t="n">
-        <v>6410667</v>
+        <v>6410721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229347</v>
+        <v>129229344</v>
       </c>
       <c r="B15" t="n">
-        <v>86944</v>
+        <v>75157</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723429</v>
+        <v>723497</v>
       </c>
       <c r="R15" t="n">
-        <v>6410682</v>
+        <v>6410619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129229348</v>
+        <v>129229329</v>
       </c>
       <c r="B16" t="n">
-        <v>86806</v>
+        <v>87008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3712</v>
+        <v>248947</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723376</v>
+        <v>723312</v>
       </c>
       <c r="R16" t="n">
-        <v>6410721</v>
+        <v>6410667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129229327</v>
+        <v>129229333</v>
       </c>
       <c r="B17" t="n">
-        <v>86806</v>
+        <v>91310</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723204</v>
+        <v>723567</v>
       </c>
       <c r="R17" t="n">
-        <v>6410629</v>
+        <v>6410767</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129229333</v>
+        <v>129229327</v>
       </c>
       <c r="B18" t="n">
-        <v>91304</v>
+        <v>86810</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723567</v>
+        <v>723204</v>
       </c>
       <c r="R18" t="n">
-        <v>6410767</v>
+        <v>6410629</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>129229357</v>
       </c>
       <c r="B19" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129229356</v>
       </c>
       <c r="B21" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>129229345</v>
       </c>
       <c r="B22" t="n">
-        <v>91304</v>
+        <v>91310</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129229325</v>
+        <v>129229359</v>
       </c>
       <c r="B23" t="n">
-        <v>75155</v>
+        <v>86948</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723224</v>
+        <v>723306</v>
       </c>
       <c r="R23" t="n">
-        <v>6410591</v>
+        <v>6410551</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129229359</v>
+        <v>129229325</v>
       </c>
       <c r="B24" t="n">
-        <v>86944</v>
+        <v>75157</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723306</v>
+        <v>723224</v>
       </c>
       <c r="R24" t="n">
-        <v>6410551</v>
+        <v>6410591</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2909,7 +2909,7 @@
         <v>129229330</v>
       </c>
       <c r="B25" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>129229338</v>
       </c>
       <c r="B26" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>129229343</v>
       </c>
       <c r="B27" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129229360</v>
       </c>
       <c r="B28" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129229356</v>
+        <v>129229345</v>
       </c>
       <c r="B21" t="n">
-        <v>86948</v>
+        <v>91310</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3674</v>
+        <v>2015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723325</v>
+        <v>723449</v>
       </c>
       <c r="R21" t="n">
-        <v>6410586</v>
+        <v>6410627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129229345</v>
+        <v>129229356</v>
       </c>
       <c r="B22" t="n">
-        <v>91310</v>
+        <v>86948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2015</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723449</v>
+        <v>723325</v>
       </c>
       <c r="R22" t="n">
-        <v>6410627</v>
+        <v>6410586</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129229355</v>
       </c>
       <c r="B2" t="n">
-        <v>87008</v>
+        <v>87015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129229341</v>
       </c>
       <c r="B3" t="n">
-        <v>87008</v>
+        <v>87015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229336</v>
+        <v>129229354</v>
       </c>
       <c r="B4" t="n">
-        <v>86832</v>
+        <v>92478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>424</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723581</v>
+        <v>723353</v>
       </c>
       <c r="R4" t="n">
-        <v>6410745</v>
+        <v>6410630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>129229351</v>
       </c>
       <c r="B5" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229354</v>
+        <v>129229336</v>
       </c>
       <c r="B6" t="n">
-        <v>92471</v>
+        <v>86839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723353</v>
+        <v>723581</v>
       </c>
       <c r="R6" t="n">
-        <v>6410630</v>
+        <v>6410745</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229342</v>
+        <v>129229337</v>
       </c>
       <c r="B7" t="n">
-        <v>86786</v>
+        <v>86817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723584</v>
+        <v>723587</v>
       </c>
       <c r="R7" t="n">
-        <v>6410681</v>
+        <v>6410736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229337</v>
+        <v>129229358</v>
       </c>
       <c r="B8" t="n">
-        <v>86810</v>
+        <v>75157</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R8" t="n">
-        <v>6410736</v>
+        <v>6410544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129229358</v>
+        <v>129229342</v>
       </c>
       <c r="B9" t="n">
-        <v>75157</v>
+        <v>86793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723311</v>
+        <v>723584</v>
       </c>
       <c r="R9" t="n">
-        <v>6410544</v>
+        <v>6410681</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92822</v>
+        <v>92829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129229335</v>
       </c>
       <c r="B11" t="n">
-        <v>87008</v>
+        <v>87015</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129229353</v>
       </c>
       <c r="B12" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129229347</v>
       </c>
       <c r="B13" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129229348</v>
       </c>
       <c r="B14" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129229329</v>
       </c>
       <c r="B16" t="n">
-        <v>87008</v>
+        <v>87015</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129229333</v>
       </c>
       <c r="B17" t="n">
-        <v>91310</v>
+        <v>91317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>129229327</v>
       </c>
       <c r="B18" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129229357</v>
       </c>
       <c r="B19" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92822</v>
+        <v>92829</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129229345</v>
       </c>
       <c r="B21" t="n">
-        <v>91310</v>
+        <v>91317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>129229356</v>
       </c>
       <c r="B22" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129229359</v>
       </c>
       <c r="B23" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>129229330</v>
       </c>
       <c r="B25" t="n">
-        <v>86832</v>
+        <v>86839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>129229338</v>
       </c>
       <c r="B26" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>129229343</v>
       </c>
       <c r="B27" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129229360</v>
       </c>
       <c r="B28" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129229355</v>
       </c>
       <c r="B2" t="n">
-        <v>87015</v>
+        <v>87017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129229341</v>
       </c>
       <c r="B3" t="n">
-        <v>87015</v>
+        <v>87017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229354</v>
+        <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>92478</v>
+        <v>86841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723353</v>
+        <v>723581</v>
       </c>
       <c r="R4" t="n">
-        <v>6410630</v>
+        <v>6410745</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>129229351</v>
       </c>
       <c r="B5" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229336</v>
+        <v>129229354</v>
       </c>
       <c r="B6" t="n">
-        <v>86839</v>
+        <v>92480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>424</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723581</v>
+        <v>723353</v>
       </c>
       <c r="R6" t="n">
-        <v>6410745</v>
+        <v>6410630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229337</v>
+        <v>129229342</v>
       </c>
       <c r="B7" t="n">
-        <v>86817</v>
+        <v>86795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723587</v>
+        <v>723584</v>
       </c>
       <c r="R7" t="n">
-        <v>6410736</v>
+        <v>6410681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229358</v>
+        <v>129229337</v>
       </c>
       <c r="B8" t="n">
-        <v>75157</v>
+        <v>86819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R8" t="n">
-        <v>6410544</v>
+        <v>6410736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129229342</v>
+        <v>129229358</v>
       </c>
       <c r="B9" t="n">
-        <v>86793</v>
+        <v>75159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723584</v>
+        <v>723311</v>
       </c>
       <c r="R9" t="n">
-        <v>6410681</v>
+        <v>6410544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129229335</v>
+        <v>129229353</v>
       </c>
       <c r="B11" t="n">
-        <v>87015</v>
+        <v>86957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>248947</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723575</v>
+        <v>723360</v>
       </c>
       <c r="R11" t="n">
-        <v>6410765</v>
+        <v>6410661</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129229353</v>
+        <v>129229335</v>
       </c>
       <c r="B12" t="n">
-        <v>86955</v>
+        <v>87017</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723360</v>
+        <v>723575</v>
       </c>
       <c r="R12" t="n">
-        <v>6410661</v>
+        <v>6410765</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>129229347</v>
       </c>
       <c r="B13" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129229348</v>
       </c>
       <c r="B14" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129229344</v>
       </c>
       <c r="B15" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129229329</v>
       </c>
       <c r="B16" t="n">
-        <v>87015</v>
+        <v>87017</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129229333</v>
       </c>
       <c r="B17" t="n">
-        <v>91317</v>
+        <v>91319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>129229327</v>
       </c>
       <c r="B18" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129229357</v>
       </c>
       <c r="B19" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129229345</v>
       </c>
       <c r="B21" t="n">
-        <v>91317</v>
+        <v>91319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>129229356</v>
       </c>
       <c r="B22" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129229359</v>
       </c>
       <c r="B23" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>129229325</v>
       </c>
       <c r="B24" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>129229330</v>
       </c>
       <c r="B25" t="n">
-        <v>86839</v>
+        <v>86841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>129229338</v>
       </c>
       <c r="B26" t="n">
-        <v>86908</v>
+        <v>86910</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>129229343</v>
       </c>
       <c r="B27" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129229360</v>
       </c>
       <c r="B28" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229336</v>
+        <v>129229351</v>
       </c>
       <c r="B4" t="n">
-        <v>86841</v>
+        <v>86819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723581</v>
+        <v>723362</v>
       </c>
       <c r="R4" t="n">
-        <v>6410745</v>
+        <v>6410659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229351</v>
+        <v>129229354</v>
       </c>
       <c r="B5" t="n">
-        <v>86819</v>
+        <v>92480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723362</v>
+        <v>723353</v>
       </c>
       <c r="R5" t="n">
-        <v>6410659</v>
+        <v>6410630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229354</v>
+        <v>129229336</v>
       </c>
       <c r="B6" t="n">
-        <v>92480</v>
+        <v>86841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723353</v>
+        <v>723581</v>
       </c>
       <c r="R6" t="n">
-        <v>6410630</v>
+        <v>6410745</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229330</v>
+        <v>129229338</v>
       </c>
       <c r="B25" t="n">
-        <v>86841</v>
+        <v>86910</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R25" t="n">
-        <v>6410669</v>
+        <v>6410736</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129229338</v>
+        <v>129229330</v>
       </c>
       <c r="B26" t="n">
-        <v>86910</v>
+        <v>86841</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R26" t="n">
-        <v>6410736</v>
+        <v>6410669</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229351</v>
+        <v>129229354</v>
       </c>
       <c r="B4" t="n">
-        <v>86819</v>
+        <v>92480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3712</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723362</v>
+        <v>723353</v>
       </c>
       <c r="R4" t="n">
-        <v>6410659</v>
+        <v>6410630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229354</v>
+        <v>129229336</v>
       </c>
       <c r="B5" t="n">
-        <v>92480</v>
+        <v>86841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723353</v>
+        <v>723581</v>
       </c>
       <c r="R5" t="n">
-        <v>6410630</v>
+        <v>6410745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229336</v>
+        <v>129229351</v>
       </c>
       <c r="B6" t="n">
-        <v>86841</v>
+        <v>86819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723581</v>
+        <v>723362</v>
       </c>
       <c r="R6" t="n">
-        <v>6410745</v>
+        <v>6410659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229338</v>
+        <v>129229330</v>
       </c>
       <c r="B25" t="n">
-        <v>86910</v>
+        <v>86841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R25" t="n">
-        <v>6410736</v>
+        <v>6410669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129229330</v>
+        <v>129229338</v>
       </c>
       <c r="B26" t="n">
-        <v>86841</v>
+        <v>86910</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R26" t="n">
-        <v>6410669</v>
+        <v>6410736</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129229355</v>
       </c>
       <c r="B2" t="n">
-        <v>87017</v>
+        <v>87018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129229341</v>
       </c>
       <c r="B3" t="n">
-        <v>87017</v>
+        <v>87018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229354</v>
+        <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>92480</v>
+        <v>86842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723353</v>
+        <v>723581</v>
       </c>
       <c r="R4" t="n">
-        <v>6410630</v>
+        <v>6410745</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229336</v>
+        <v>129229351</v>
       </c>
       <c r="B5" t="n">
-        <v>86841</v>
+        <v>86820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723581</v>
+        <v>723362</v>
       </c>
       <c r="R5" t="n">
-        <v>6410745</v>
+        <v>6410659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229351</v>
+        <v>129229354</v>
       </c>
       <c r="B6" t="n">
-        <v>86819</v>
+        <v>92494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3712</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723362</v>
+        <v>723353</v>
       </c>
       <c r="R6" t="n">
-        <v>6410659</v>
+        <v>6410630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229342</v>
+        <v>129229358</v>
       </c>
       <c r="B7" t="n">
-        <v>86795</v>
+        <v>75159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723584</v>
+        <v>723311</v>
       </c>
       <c r="R7" t="n">
-        <v>6410681</v>
+        <v>6410544</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229337</v>
+        <v>129229342</v>
       </c>
       <c r="B8" t="n">
-        <v>86819</v>
+        <v>86796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723587</v>
+        <v>723584</v>
       </c>
       <c r="R8" t="n">
-        <v>6410736</v>
+        <v>6410681</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129229358</v>
+        <v>129229337</v>
       </c>
       <c r="B9" t="n">
-        <v>75159</v>
+        <v>86820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>3712</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R9" t="n">
-        <v>6410544</v>
+        <v>6410736</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92831</v>
+        <v>92817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129229353</v>
       </c>
       <c r="B11" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129229335</v>
       </c>
       <c r="B12" t="n">
-        <v>87017</v>
+        <v>87018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229347</v>
+        <v>129229329</v>
       </c>
       <c r="B13" t="n">
-        <v>86957</v>
+        <v>87018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723429</v>
+        <v>723312</v>
       </c>
       <c r="R13" t="n">
-        <v>6410682</v>
+        <v>6410667</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129229348</v>
+        <v>129229347</v>
       </c>
       <c r="B14" t="n">
-        <v>86819</v>
+        <v>86958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723376</v>
+        <v>723429</v>
       </c>
       <c r="R14" t="n">
-        <v>6410721</v>
+        <v>6410682</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229344</v>
+        <v>129229348</v>
       </c>
       <c r="B15" t="n">
-        <v>75159</v>
+        <v>86820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>3712</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723497</v>
+        <v>723376</v>
       </c>
       <c r="R15" t="n">
-        <v>6410619</v>
+        <v>6410721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129229329</v>
+        <v>129229344</v>
       </c>
       <c r="B16" t="n">
-        <v>87017</v>
+        <v>75159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248947</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723312</v>
+        <v>723497</v>
       </c>
       <c r="R16" t="n">
-        <v>6410667</v>
+        <v>6410619</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>129229333</v>
       </c>
       <c r="B17" t="n">
-        <v>91319</v>
+        <v>91318</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>129229327</v>
       </c>
       <c r="B18" t="n">
-        <v>86819</v>
+        <v>86820</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129229357</v>
       </c>
       <c r="B19" t="n">
-        <v>86819</v>
+        <v>86820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92831</v>
+        <v>92817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129229345</v>
       </c>
       <c r="B21" t="n">
-        <v>91319</v>
+        <v>91318</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>129229356</v>
       </c>
       <c r="B22" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129229359</v>
       </c>
       <c r="B23" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>129229330</v>
       </c>
       <c r="B25" t="n">
-        <v>86841</v>
+        <v>86842</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>129229338</v>
       </c>
       <c r="B26" t="n">
-        <v>86910</v>
+        <v>86911</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>129229343</v>
       </c>
       <c r="B27" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129229360</v>
       </c>
       <c r="B28" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229336</v>
+        <v>129229354</v>
       </c>
       <c r="B4" t="n">
-        <v>86842</v>
+        <v>92495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>424</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723581</v>
+        <v>723353</v>
       </c>
       <c r="R4" t="n">
-        <v>6410745</v>
+        <v>6410630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229354</v>
+        <v>129229336</v>
       </c>
       <c r="B6" t="n">
-        <v>92494</v>
+        <v>86842</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723353</v>
+        <v>723581</v>
       </c>
       <c r="R6" t="n">
-        <v>6410630</v>
+        <v>6410745</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229358</v>
+        <v>129229342</v>
       </c>
       <c r="B7" t="n">
-        <v>75159</v>
+        <v>86796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723311</v>
+        <v>723584</v>
       </c>
       <c r="R7" t="n">
-        <v>6410544</v>
+        <v>6410681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229342</v>
+        <v>129229337</v>
       </c>
       <c r="B8" t="n">
-        <v>86796</v>
+        <v>86820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723584</v>
+        <v>723587</v>
       </c>
       <c r="R8" t="n">
-        <v>6410681</v>
+        <v>6410736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129229337</v>
+        <v>129229358</v>
       </c>
       <c r="B9" t="n">
-        <v>86820</v>
+        <v>75159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3712</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R9" t="n">
-        <v>6410736</v>
+        <v>6410544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92817</v>
+        <v>92818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229329</v>
+        <v>129229347</v>
       </c>
       <c r="B13" t="n">
-        <v>87018</v>
+        <v>86958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>248947</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723312</v>
+        <v>723429</v>
       </c>
       <c r="R13" t="n">
-        <v>6410667</v>
+        <v>6410682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129229347</v>
+        <v>129229348</v>
       </c>
       <c r="B14" t="n">
-        <v>86958</v>
+        <v>86820</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723429</v>
+        <v>723376</v>
       </c>
       <c r="R14" t="n">
-        <v>6410682</v>
+        <v>6410721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229348</v>
+        <v>129229344</v>
       </c>
       <c r="B15" t="n">
-        <v>86820</v>
+        <v>75159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3712</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723376</v>
+        <v>723497</v>
       </c>
       <c r="R15" t="n">
-        <v>6410721</v>
+        <v>6410619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129229344</v>
+        <v>129229329</v>
       </c>
       <c r="B16" t="n">
-        <v>75159</v>
+        <v>87018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>248947</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723497</v>
+        <v>723312</v>
       </c>
       <c r="R16" t="n">
-        <v>6410619</v>
+        <v>6410667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92817</v>
+        <v>92818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229354</v>
+        <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>92495</v>
+        <v>86842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723353</v>
+        <v>723581</v>
       </c>
       <c r="R4" t="n">
-        <v>6410630</v>
+        <v>6410745</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229336</v>
+        <v>129229354</v>
       </c>
       <c r="B6" t="n">
-        <v>86842</v>
+        <v>92495</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>424</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723581</v>
+        <v>723353</v>
       </c>
       <c r="R6" t="n">
-        <v>6410745</v>
+        <v>6410630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229342</v>
+        <v>129229337</v>
       </c>
       <c r="B7" t="n">
-        <v>86796</v>
+        <v>86820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723584</v>
+        <v>723587</v>
       </c>
       <c r="R7" t="n">
-        <v>6410681</v>
+        <v>6410736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229337</v>
+        <v>129229342</v>
       </c>
       <c r="B8" t="n">
-        <v>86820</v>
+        <v>86796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723587</v>
+        <v>723584</v>
       </c>
       <c r="R8" t="n">
-        <v>6410736</v>
+        <v>6410681</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129229355</v>
       </c>
       <c r="B2" t="n">
-        <v>87018</v>
+        <v>87021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129229341</v>
       </c>
       <c r="B3" t="n">
-        <v>87018</v>
+        <v>87021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>86842</v>
+        <v>86845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129229351</v>
       </c>
       <c r="B5" t="n">
-        <v>86820</v>
+        <v>86823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129229354</v>
       </c>
       <c r="B6" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229337</v>
+        <v>129229342</v>
       </c>
       <c r="B7" t="n">
-        <v>86820</v>
+        <v>86799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723587</v>
+        <v>723584</v>
       </c>
       <c r="R7" t="n">
-        <v>6410736</v>
+        <v>6410681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229342</v>
+        <v>129229337</v>
       </c>
       <c r="B8" t="n">
-        <v>86796</v>
+        <v>86823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723584</v>
+        <v>723587</v>
       </c>
       <c r="R8" t="n">
-        <v>6410681</v>
+        <v>6410736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>129229358</v>
       </c>
       <c r="B9" t="n">
-        <v>75159</v>
+        <v>75161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92818</v>
+        <v>92821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129229353</v>
+        <v>129229335</v>
       </c>
       <c r="B11" t="n">
-        <v>86958</v>
+        <v>87021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723360</v>
+        <v>723575</v>
       </c>
       <c r="R11" t="n">
-        <v>6410661</v>
+        <v>6410765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129229335</v>
+        <v>129229353</v>
       </c>
       <c r="B12" t="n">
-        <v>87018</v>
+        <v>86961</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>248947</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723575</v>
+        <v>723360</v>
       </c>
       <c r="R12" t="n">
-        <v>6410765</v>
+        <v>6410661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229347</v>
+        <v>129229344</v>
       </c>
       <c r="B13" t="n">
-        <v>86958</v>
+        <v>75161</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723429</v>
+        <v>723497</v>
       </c>
       <c r="R13" t="n">
-        <v>6410682</v>
+        <v>6410619</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129229348</v>
+        <v>129229347</v>
       </c>
       <c r="B14" t="n">
-        <v>86820</v>
+        <v>86961</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723376</v>
+        <v>723429</v>
       </c>
       <c r="R14" t="n">
-        <v>6410721</v>
+        <v>6410682</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229344</v>
+        <v>129229348</v>
       </c>
       <c r="B15" t="n">
-        <v>75159</v>
+        <v>86823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>3712</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723497</v>
+        <v>723376</v>
       </c>
       <c r="R15" t="n">
-        <v>6410619</v>
+        <v>6410721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>129229329</v>
       </c>
       <c r="B16" t="n">
-        <v>87018</v>
+        <v>87021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129229333</v>
       </c>
       <c r="B17" t="n">
-        <v>91318</v>
+        <v>91321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>129229327</v>
       </c>
       <c r="B18" t="n">
-        <v>86820</v>
+        <v>86823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129229357</v>
       </c>
       <c r="B19" t="n">
-        <v>86820</v>
+        <v>86823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92818</v>
+        <v>92821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129229345</v>
       </c>
       <c r="B21" t="n">
-        <v>91318</v>
+        <v>91321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>129229356</v>
       </c>
       <c r="B22" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129229359</v>
       </c>
       <c r="B23" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>129229325</v>
       </c>
       <c r="B24" t="n">
-        <v>75159</v>
+        <v>75161</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229330</v>
+        <v>129229338</v>
       </c>
       <c r="B25" t="n">
-        <v>86842</v>
+        <v>86914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R25" t="n">
-        <v>6410669</v>
+        <v>6410736</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129229338</v>
+        <v>129229330</v>
       </c>
       <c r="B26" t="n">
-        <v>86911</v>
+        <v>86845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R26" t="n">
-        <v>6410736</v>
+        <v>6410669</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3103,7 +3103,7 @@
         <v>129229343</v>
       </c>
       <c r="B27" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129229360</v>
       </c>
       <c r="B28" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129229355</v>
       </c>
       <c r="B2" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129229341</v>
       </c>
       <c r="B3" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>86845</v>
+        <v>86847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129229351</v>
       </c>
       <c r="B5" t="n">
-        <v>86823</v>
+        <v>86825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129229354</v>
       </c>
       <c r="B6" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229342</v>
+        <v>129229358</v>
       </c>
       <c r="B7" t="n">
-        <v>86799</v>
+        <v>75161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723584</v>
+        <v>723311</v>
       </c>
       <c r="R7" t="n">
-        <v>6410681</v>
+        <v>6410544</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229337</v>
+        <v>129229342</v>
       </c>
       <c r="B8" t="n">
-        <v>86823</v>
+        <v>86801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723587</v>
+        <v>723584</v>
       </c>
       <c r="R8" t="n">
-        <v>6410736</v>
+        <v>6410681</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129229358</v>
+        <v>129229337</v>
       </c>
       <c r="B9" t="n">
-        <v>75161</v>
+        <v>86825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>3712</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R9" t="n">
-        <v>6410544</v>
+        <v>6410736</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129229335</v>
+        <v>129229353</v>
       </c>
       <c r="B11" t="n">
-        <v>87021</v>
+        <v>86963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>248947</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723575</v>
+        <v>723360</v>
       </c>
       <c r="R11" t="n">
-        <v>6410765</v>
+        <v>6410661</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129229353</v>
+        <v>129229335</v>
       </c>
       <c r="B12" t="n">
-        <v>86961</v>
+        <v>87023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723360</v>
+        <v>723575</v>
       </c>
       <c r="R12" t="n">
-        <v>6410661</v>
+        <v>6410765</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229344</v>
+        <v>129229347</v>
       </c>
       <c r="B13" t="n">
-        <v>75161</v>
+        <v>86963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723497</v>
+        <v>723429</v>
       </c>
       <c r="R13" t="n">
-        <v>6410619</v>
+        <v>6410682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129229347</v>
+        <v>129229348</v>
       </c>
       <c r="B14" t="n">
-        <v>86961</v>
+        <v>86825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723429</v>
+        <v>723376</v>
       </c>
       <c r="R14" t="n">
-        <v>6410682</v>
+        <v>6410721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229348</v>
+        <v>129229344</v>
       </c>
       <c r="B15" t="n">
-        <v>86823</v>
+        <v>75161</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3712</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723376</v>
+        <v>723497</v>
       </c>
       <c r="R15" t="n">
-        <v>6410721</v>
+        <v>6410619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>129229329</v>
       </c>
       <c r="B16" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129229333</v>
       </c>
       <c r="B17" t="n">
-        <v>91321</v>
+        <v>91323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>129229327</v>
       </c>
       <c r="B18" t="n">
-        <v>86823</v>
+        <v>86825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129229357</v>
       </c>
       <c r="B19" t="n">
-        <v>86823</v>
+        <v>86825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129229345</v>
       </c>
       <c r="B21" t="n">
-        <v>91321</v>
+        <v>91323</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>129229356</v>
       </c>
       <c r="B22" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129229359</v>
       </c>
       <c r="B23" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229338</v>
+        <v>129229330</v>
       </c>
       <c r="B25" t="n">
-        <v>86914</v>
+        <v>86847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R25" t="n">
-        <v>6410736</v>
+        <v>6410669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129229330</v>
+        <v>129229338</v>
       </c>
       <c r="B26" t="n">
-        <v>86845</v>
+        <v>86916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R26" t="n">
-        <v>6410669</v>
+        <v>6410736</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3103,7 +3103,7 @@
         <v>129229343</v>
       </c>
       <c r="B27" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129229360</v>
       </c>
       <c r="B28" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129229355</v>
       </c>
       <c r="B2" t="n">
-        <v>87023</v>
+        <v>87027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129229341</v>
       </c>
       <c r="B3" t="n">
-        <v>87023</v>
+        <v>87027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>86847</v>
+        <v>86851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229351</v>
+        <v>129229354</v>
       </c>
       <c r="B5" t="n">
-        <v>86825</v>
+        <v>92504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723362</v>
+        <v>723353</v>
       </c>
       <c r="R5" t="n">
-        <v>6410659</v>
+        <v>6410630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229354</v>
+        <v>129229351</v>
       </c>
       <c r="B6" t="n">
-        <v>92500</v>
+        <v>86829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723353</v>
+        <v>723362</v>
       </c>
       <c r="R6" t="n">
-        <v>6410630</v>
+        <v>6410659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>129229342</v>
       </c>
       <c r="B8" t="n">
-        <v>86801</v>
+        <v>86805</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>129229337</v>
       </c>
       <c r="B9" t="n">
-        <v>86825</v>
+        <v>86829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129229353</v>
       </c>
       <c r="B11" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129229335</v>
       </c>
       <c r="B12" t="n">
-        <v>87023</v>
+        <v>87027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>129229347</v>
       </c>
       <c r="B13" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>129229348</v>
       </c>
       <c r="B14" t="n">
-        <v>86825</v>
+        <v>86829</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129229329</v>
       </c>
       <c r="B16" t="n">
-        <v>87023</v>
+        <v>87027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129229333</v>
+        <v>129229327</v>
       </c>
       <c r="B17" t="n">
-        <v>91323</v>
+        <v>86829</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723567</v>
+        <v>723204</v>
       </c>
       <c r="R17" t="n">
-        <v>6410767</v>
+        <v>6410629</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129229327</v>
+        <v>129229333</v>
       </c>
       <c r="B18" t="n">
-        <v>86825</v>
+        <v>91327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723204</v>
+        <v>723567</v>
       </c>
       <c r="R18" t="n">
-        <v>6410629</v>
+        <v>6410767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>129229357</v>
       </c>
       <c r="B19" t="n">
-        <v>86825</v>
+        <v>86829</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129229345</v>
+        <v>129229356</v>
       </c>
       <c r="B21" t="n">
-        <v>91323</v>
+        <v>86967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2015</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723449</v>
+        <v>723325</v>
       </c>
       <c r="R21" t="n">
-        <v>6410627</v>
+        <v>6410586</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129229356</v>
+        <v>129229345</v>
       </c>
       <c r="B22" t="n">
-        <v>86963</v>
+        <v>91327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>2015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723325</v>
+        <v>723449</v>
       </c>
       <c r="R22" t="n">
-        <v>6410586</v>
+        <v>6410627</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129229359</v>
+        <v>129229325</v>
       </c>
       <c r="B23" t="n">
-        <v>86963</v>
+        <v>75161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723306</v>
+        <v>723224</v>
       </c>
       <c r="R23" t="n">
-        <v>6410551</v>
+        <v>6410591</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129229325</v>
+        <v>129229359</v>
       </c>
       <c r="B24" t="n">
-        <v>75161</v>
+        <v>86967</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723224</v>
+        <v>723306</v>
       </c>
       <c r="R24" t="n">
-        <v>6410591</v>
+        <v>6410551</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229330</v>
+        <v>129229338</v>
       </c>
       <c r="B25" t="n">
-        <v>86847</v>
+        <v>86920</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R25" t="n">
-        <v>6410669</v>
+        <v>6410736</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129229338</v>
+        <v>129229330</v>
       </c>
       <c r="B26" t="n">
-        <v>86916</v>
+        <v>86851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R26" t="n">
-        <v>6410736</v>
+        <v>6410669</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3103,7 +3103,7 @@
         <v>129229343</v>
       </c>
       <c r="B27" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129229360</v>
       </c>
       <c r="B28" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129229355</v>
       </c>
       <c r="B2" t="n">
-        <v>87027</v>
+        <v>87028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129229341</v>
       </c>
       <c r="B3" t="n">
-        <v>87027</v>
+        <v>87028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229336</v>
+        <v>129229354</v>
       </c>
       <c r="B4" t="n">
-        <v>86851</v>
+        <v>92505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>424</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723581</v>
+        <v>723353</v>
       </c>
       <c r="R4" t="n">
-        <v>6410745</v>
+        <v>6410630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229354</v>
+        <v>129229336</v>
       </c>
       <c r="B5" t="n">
-        <v>92504</v>
+        <v>86852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723353</v>
+        <v>723581</v>
       </c>
       <c r="R5" t="n">
-        <v>6410630</v>
+        <v>6410745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129229351</v>
       </c>
       <c r="B6" t="n">
-        <v>86829</v>
+        <v>86830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229358</v>
+        <v>129229337</v>
       </c>
       <c r="B7" t="n">
-        <v>75161</v>
+        <v>86830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R7" t="n">
-        <v>6410544</v>
+        <v>6410736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>129229342</v>
       </c>
       <c r="B8" t="n">
-        <v>86805</v>
+        <v>86806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129229337</v>
+        <v>129229358</v>
       </c>
       <c r="B9" t="n">
-        <v>86829</v>
+        <v>75161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3712</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R9" t="n">
-        <v>6410736</v>
+        <v>6410544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92827</v>
+        <v>92828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129229353</v>
       </c>
       <c r="B11" t="n">
-        <v>86967</v>
+        <v>86968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129229335</v>
       </c>
       <c r="B12" t="n">
-        <v>87027</v>
+        <v>87028</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229347</v>
+        <v>129229344</v>
       </c>
       <c r="B13" t="n">
-        <v>86967</v>
+        <v>75161</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723429</v>
+        <v>723497</v>
       </c>
       <c r="R13" t="n">
-        <v>6410682</v>
+        <v>6410619</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129229348</v>
+        <v>129229329</v>
       </c>
       <c r="B14" t="n">
-        <v>86829</v>
+        <v>87028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3712</v>
+        <v>248947</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723376</v>
+        <v>723312</v>
       </c>
       <c r="R14" t="n">
-        <v>6410721</v>
+        <v>6410667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229344</v>
+        <v>129229347</v>
       </c>
       <c r="B15" t="n">
-        <v>75161</v>
+        <v>86968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723497</v>
+        <v>723429</v>
       </c>
       <c r="R15" t="n">
-        <v>6410619</v>
+        <v>6410682</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129229329</v>
+        <v>129229348</v>
       </c>
       <c r="B16" t="n">
-        <v>87027</v>
+        <v>86830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723312</v>
+        <v>723376</v>
       </c>
       <c r="R16" t="n">
-        <v>6410667</v>
+        <v>6410721</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>129229327</v>
       </c>
       <c r="B17" t="n">
-        <v>86829</v>
+        <v>86830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>129229333</v>
       </c>
       <c r="B18" t="n">
-        <v>91327</v>
+        <v>91328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129229357</v>
       </c>
       <c r="B19" t="n">
-        <v>86829</v>
+        <v>86830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92827</v>
+        <v>92828</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129229356</v>
+        <v>129229345</v>
       </c>
       <c r="B21" t="n">
-        <v>86967</v>
+        <v>91328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3674</v>
+        <v>2015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723325</v>
+        <v>723449</v>
       </c>
       <c r="R21" t="n">
-        <v>6410586</v>
+        <v>6410627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129229345</v>
+        <v>129229356</v>
       </c>
       <c r="B22" t="n">
-        <v>91327</v>
+        <v>86968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2015</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723449</v>
+        <v>723325</v>
       </c>
       <c r="R22" t="n">
-        <v>6410627</v>
+        <v>6410586</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129229325</v>
+        <v>129229359</v>
       </c>
       <c r="B23" t="n">
-        <v>75161</v>
+        <v>86968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723224</v>
+        <v>723306</v>
       </c>
       <c r="R23" t="n">
-        <v>6410591</v>
+        <v>6410551</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129229359</v>
+        <v>129229325</v>
       </c>
       <c r="B24" t="n">
-        <v>86967</v>
+        <v>75161</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723306</v>
+        <v>723224</v>
       </c>
       <c r="R24" t="n">
-        <v>6410551</v>
+        <v>6410591</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2909,7 +2909,7 @@
         <v>129229338</v>
       </c>
       <c r="B25" t="n">
-        <v>86920</v>
+        <v>86921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>129229330</v>
       </c>
       <c r="B26" t="n">
-        <v>86851</v>
+        <v>86852</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>129229343</v>
       </c>
       <c r="B27" t="n">
-        <v>86967</v>
+        <v>86968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129229360</v>
       </c>
       <c r="B28" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229354</v>
+        <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>92505</v>
+        <v>86852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723353</v>
+        <v>723581</v>
       </c>
       <c r="R4" t="n">
-        <v>6410630</v>
+        <v>6410745</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229336</v>
+        <v>129229354</v>
       </c>
       <c r="B5" t="n">
-        <v>86852</v>
+        <v>92505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>424</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723581</v>
+        <v>723353</v>
       </c>
       <c r="R5" t="n">
-        <v>6410745</v>
+        <v>6410630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229337</v>
+        <v>129229342</v>
       </c>
       <c r="B7" t="n">
-        <v>86830</v>
+        <v>86806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723587</v>
+        <v>723584</v>
       </c>
       <c r="R7" t="n">
-        <v>6410736</v>
+        <v>6410681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229342</v>
+        <v>129229337</v>
       </c>
       <c r="B8" t="n">
-        <v>86806</v>
+        <v>86830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723584</v>
+        <v>723587</v>
       </c>
       <c r="R8" t="n">
-        <v>6410681</v>
+        <v>6410736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229344</v>
+        <v>129229347</v>
       </c>
       <c r="B13" t="n">
-        <v>75161</v>
+        <v>86968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723497</v>
+        <v>723429</v>
       </c>
       <c r="R13" t="n">
-        <v>6410619</v>
+        <v>6410682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129229329</v>
+        <v>129229348</v>
       </c>
       <c r="B14" t="n">
-        <v>87028</v>
+        <v>86830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723312</v>
+        <v>723376</v>
       </c>
       <c r="R14" t="n">
-        <v>6410667</v>
+        <v>6410721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229347</v>
+        <v>129229344</v>
       </c>
       <c r="B15" t="n">
-        <v>86968</v>
+        <v>75161</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723429</v>
+        <v>723497</v>
       </c>
       <c r="R15" t="n">
-        <v>6410682</v>
+        <v>6410619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129229348</v>
+        <v>129229329</v>
       </c>
       <c r="B16" t="n">
-        <v>86830</v>
+        <v>87028</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3712</v>
+        <v>248947</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723376</v>
+        <v>723312</v>
       </c>
       <c r="R16" t="n">
-        <v>6410721</v>
+        <v>6410667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129229327</v>
+        <v>129229333</v>
       </c>
       <c r="B17" t="n">
-        <v>86830</v>
+        <v>91328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723204</v>
+        <v>723567</v>
       </c>
       <c r="R17" t="n">
-        <v>6410629</v>
+        <v>6410767</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129229333</v>
+        <v>129229327</v>
       </c>
       <c r="B18" t="n">
-        <v>91328</v>
+        <v>86830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723567</v>
+        <v>723204</v>
       </c>
       <c r="R18" t="n">
-        <v>6410767</v>
+        <v>6410629</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229338</v>
+        <v>129229330</v>
       </c>
       <c r="B25" t="n">
-        <v>86921</v>
+        <v>86852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R25" t="n">
-        <v>6410736</v>
+        <v>6410669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129229330</v>
+        <v>129229338</v>
       </c>
       <c r="B26" t="n">
-        <v>86852</v>
+        <v>86921</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R26" t="n">
-        <v>6410669</v>
+        <v>6410736</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129229353</v>
+        <v>129229335</v>
       </c>
       <c r="B11" t="n">
-        <v>86968</v>
+        <v>87028</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723360</v>
+        <v>723575</v>
       </c>
       <c r="R11" t="n">
-        <v>6410661</v>
+        <v>6410765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129229335</v>
+        <v>129229353</v>
       </c>
       <c r="B12" t="n">
-        <v>87028</v>
+        <v>86968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>248947</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723575</v>
+        <v>723360</v>
       </c>
       <c r="R12" t="n">
-        <v>6410765</v>
+        <v>6410661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229354</v>
+        <v>129229351</v>
       </c>
       <c r="B5" t="n">
-        <v>92505</v>
+        <v>86830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723353</v>
+        <v>723362</v>
       </c>
       <c r="R5" t="n">
-        <v>6410630</v>
+        <v>6410659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229351</v>
+        <v>129229354</v>
       </c>
       <c r="B6" t="n">
-        <v>86830</v>
+        <v>92508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3712</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723362</v>
+        <v>723353</v>
       </c>
       <c r="R6" t="n">
-        <v>6410659</v>
+        <v>6410630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129229333</v>
       </c>
       <c r="B17" t="n">
-        <v>91328</v>
+        <v>91331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129229345</v>
       </c>
       <c r="B21" t="n">
-        <v>91328</v>
+        <v>91331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229336</v>
+        <v>129229351</v>
       </c>
       <c r="B4" t="n">
-        <v>86852</v>
+        <v>86830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723581</v>
+        <v>723362</v>
       </c>
       <c r="R4" t="n">
-        <v>6410745</v>
+        <v>6410659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229351</v>
+        <v>129229336</v>
       </c>
       <c r="B5" t="n">
-        <v>86830</v>
+        <v>86852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723362</v>
+        <v>723581</v>
       </c>
       <c r="R5" t="n">
-        <v>6410659</v>
+        <v>6410745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129229335</v>
+        <v>129229353</v>
       </c>
       <c r="B11" t="n">
-        <v>87028</v>
+        <v>86968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>248947</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723575</v>
+        <v>723360</v>
       </c>
       <c r="R11" t="n">
-        <v>6410765</v>
+        <v>6410661</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129229353</v>
+        <v>129229335</v>
       </c>
       <c r="B12" t="n">
-        <v>86968</v>
+        <v>87028</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723360</v>
+        <v>723575</v>
       </c>
       <c r="R12" t="n">
-        <v>6410661</v>
+        <v>6410765</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229347</v>
+        <v>129229344</v>
       </c>
       <c r="B13" t="n">
-        <v>86968</v>
+        <v>75161</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723429</v>
+        <v>723497</v>
       </c>
       <c r="R13" t="n">
-        <v>6410682</v>
+        <v>6410619</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229344</v>
+        <v>129229347</v>
       </c>
       <c r="B15" t="n">
-        <v>75161</v>
+        <v>86968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723497</v>
+        <v>723429</v>
       </c>
       <c r="R15" t="n">
-        <v>6410619</v>
+        <v>6410682</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129229333</v>
+        <v>129229327</v>
       </c>
       <c r="B17" t="n">
-        <v>91331</v>
+        <v>86830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723567</v>
+        <v>723204</v>
       </c>
       <c r="R17" t="n">
-        <v>6410767</v>
+        <v>6410629</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129229327</v>
+        <v>129229333</v>
       </c>
       <c r="B18" t="n">
-        <v>86830</v>
+        <v>91331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723204</v>
+        <v>723567</v>
       </c>
       <c r="R18" t="n">
-        <v>6410629</v>
+        <v>6410767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129229359</v>
+        <v>129229325</v>
       </c>
       <c r="B23" t="n">
-        <v>86968</v>
+        <v>75161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723306</v>
+        <v>723224</v>
       </c>
       <c r="R23" t="n">
-        <v>6410551</v>
+        <v>6410591</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129229325</v>
+        <v>129229359</v>
       </c>
       <c r="B24" t="n">
-        <v>75161</v>
+        <v>86968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723224</v>
+        <v>723306</v>
       </c>
       <c r="R24" t="n">
-        <v>6410591</v>
+        <v>6410551</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229351</v>
+        <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>86830</v>
+        <v>86852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723362</v>
+        <v>723581</v>
       </c>
       <c r="R4" t="n">
-        <v>6410659</v>
+        <v>6410745</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229336</v>
+        <v>129229351</v>
       </c>
       <c r="B5" t="n">
-        <v>86852</v>
+        <v>86830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723581</v>
+        <v>723362</v>
       </c>
       <c r="R5" t="n">
-        <v>6410745</v>
+        <v>6410659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229342</v>
+        <v>129229337</v>
       </c>
       <c r="B7" t="n">
-        <v>86806</v>
+        <v>86830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723584</v>
+        <v>723587</v>
       </c>
       <c r="R7" t="n">
-        <v>6410681</v>
+        <v>6410736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229337</v>
+        <v>129229342</v>
       </c>
       <c r="B8" t="n">
-        <v>86830</v>
+        <v>86806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723587</v>
+        <v>723584</v>
       </c>
       <c r="R8" t="n">
-        <v>6410736</v>
+        <v>6410681</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229344</v>
+        <v>129229347</v>
       </c>
       <c r="B13" t="n">
-        <v>75161</v>
+        <v>86968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723497</v>
+        <v>723429</v>
       </c>
       <c r="R13" t="n">
-        <v>6410619</v>
+        <v>6410682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229347</v>
+        <v>129229344</v>
       </c>
       <c r="B15" t="n">
-        <v>86968</v>
+        <v>75161</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723429</v>
+        <v>723497</v>
       </c>
       <c r="R15" t="n">
-        <v>6410682</v>
+        <v>6410619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129229345</v>
+        <v>129229356</v>
       </c>
       <c r="B21" t="n">
-        <v>91331</v>
+        <v>86968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2015</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723449</v>
+        <v>723325</v>
       </c>
       <c r="R21" t="n">
-        <v>6410627</v>
+        <v>6410586</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129229356</v>
+        <v>129229345</v>
       </c>
       <c r="B22" t="n">
-        <v>86968</v>
+        <v>91331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>2015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723325</v>
+        <v>723449</v>
       </c>
       <c r="R22" t="n">
-        <v>6410586</v>
+        <v>6410627</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229336</v>
+        <v>129229354</v>
       </c>
       <c r="B4" t="n">
-        <v>86852</v>
+        <v>92508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>424</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723581</v>
+        <v>723353</v>
       </c>
       <c r="R4" t="n">
-        <v>6410745</v>
+        <v>6410630</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229351</v>
+        <v>129229336</v>
       </c>
       <c r="B5" t="n">
-        <v>86830</v>
+        <v>86852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723362</v>
+        <v>723581</v>
       </c>
       <c r="R5" t="n">
-        <v>6410659</v>
+        <v>6410745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229354</v>
+        <v>129229351</v>
       </c>
       <c r="B6" t="n">
-        <v>92508</v>
+        <v>86830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723353</v>
+        <v>723362</v>
       </c>
       <c r="R6" t="n">
-        <v>6410630</v>
+        <v>6410659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229337</v>
+        <v>129229358</v>
       </c>
       <c r="B7" t="n">
-        <v>86830</v>
+        <v>75161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R7" t="n">
-        <v>6410736</v>
+        <v>6410544</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229342</v>
+        <v>129229337</v>
       </c>
       <c r="B8" t="n">
-        <v>86806</v>
+        <v>86830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723584</v>
+        <v>723587</v>
       </c>
       <c r="R8" t="n">
-        <v>6410681</v>
+        <v>6410736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129229358</v>
+        <v>129229342</v>
       </c>
       <c r="B9" t="n">
-        <v>75161</v>
+        <v>86806</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723311</v>
+        <v>723584</v>
       </c>
       <c r="R9" t="n">
-        <v>6410544</v>
+        <v>6410681</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229347</v>
+        <v>129229329</v>
       </c>
       <c r="B13" t="n">
-        <v>86968</v>
+        <v>87028</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723429</v>
+        <v>723312</v>
       </c>
       <c r="R13" t="n">
-        <v>6410682</v>
+        <v>6410667</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129229348</v>
+        <v>129229344</v>
       </c>
       <c r="B14" t="n">
-        <v>86830</v>
+        <v>75161</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3712</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723376</v>
+        <v>723497</v>
       </c>
       <c r="R14" t="n">
-        <v>6410721</v>
+        <v>6410619</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229344</v>
+        <v>129229347</v>
       </c>
       <c r="B15" t="n">
-        <v>75161</v>
+        <v>86968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723497</v>
+        <v>723429</v>
       </c>
       <c r="R15" t="n">
-        <v>6410619</v>
+        <v>6410682</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129229329</v>
+        <v>129229348</v>
       </c>
       <c r="B16" t="n">
-        <v>87028</v>
+        <v>86830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723312</v>
+        <v>723376</v>
       </c>
       <c r="R16" t="n">
-        <v>6410667</v>
+        <v>6410721</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129229327</v>
+        <v>129229333</v>
       </c>
       <c r="B17" t="n">
-        <v>86830</v>
+        <v>91331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723204</v>
+        <v>723567</v>
       </c>
       <c r="R17" t="n">
-        <v>6410629</v>
+        <v>6410767</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129229333</v>
+        <v>129229327</v>
       </c>
       <c r="B18" t="n">
-        <v>91331</v>
+        <v>86830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723567</v>
+        <v>723204</v>
       </c>
       <c r="R18" t="n">
-        <v>6410767</v>
+        <v>6410629</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229330</v>
+        <v>129229338</v>
       </c>
       <c r="B25" t="n">
-        <v>86852</v>
+        <v>86921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R25" t="n">
-        <v>6410669</v>
+        <v>6410736</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129229338</v>
+        <v>129229330</v>
       </c>
       <c r="B26" t="n">
-        <v>86921</v>
+        <v>86852</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R26" t="n">
-        <v>6410736</v>
+        <v>6410669</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229354</v>
+        <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>92508</v>
+        <v>86852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723353</v>
+        <v>723581</v>
       </c>
       <c r="R4" t="n">
-        <v>6410630</v>
+        <v>6410745</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229336</v>
+        <v>129229351</v>
       </c>
       <c r="B5" t="n">
-        <v>86852</v>
+        <v>86830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723581</v>
+        <v>723362</v>
       </c>
       <c r="R5" t="n">
-        <v>6410745</v>
+        <v>6410659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229351</v>
+        <v>129229354</v>
       </c>
       <c r="B6" t="n">
-        <v>86830</v>
+        <v>92508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3712</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723362</v>
+        <v>723353</v>
       </c>
       <c r="R6" t="n">
-        <v>6410659</v>
+        <v>6410630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229329</v>
+        <v>129229344</v>
       </c>
       <c r="B13" t="n">
-        <v>87028</v>
+        <v>75161</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>248947</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723312</v>
+        <v>723497</v>
       </c>
       <c r="R13" t="n">
-        <v>6410667</v>
+        <v>6410619</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129229344</v>
+        <v>129229329</v>
       </c>
       <c r="B14" t="n">
-        <v>75161</v>
+        <v>87028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>248947</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723497</v>
+        <v>723312</v>
       </c>
       <c r="R14" t="n">
-        <v>6410619</v>
+        <v>6410667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129229333</v>
+        <v>129229327</v>
       </c>
       <c r="B17" t="n">
-        <v>91331</v>
+        <v>86830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723567</v>
+        <v>723204</v>
       </c>
       <c r="R17" t="n">
-        <v>6410767</v>
+        <v>6410629</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129229327</v>
+        <v>129229333</v>
       </c>
       <c r="B18" t="n">
-        <v>86830</v>
+        <v>91331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723204</v>
+        <v>723567</v>
       </c>
       <c r="R18" t="n">
-        <v>6410629</v>
+        <v>6410767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229338</v>
+        <v>129229330</v>
       </c>
       <c r="B25" t="n">
-        <v>86921</v>
+        <v>86852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723587</v>
+        <v>723311</v>
       </c>
       <c r="R25" t="n">
-        <v>6410736</v>
+        <v>6410669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129229330</v>
+        <v>129229338</v>
       </c>
       <c r="B26" t="n">
-        <v>86852</v>
+        <v>86921</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723311</v>
+        <v>723587</v>
       </c>
       <c r="R26" t="n">
-        <v>6410669</v>
+        <v>6410736</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229351</v>
+        <v>129229354</v>
       </c>
       <c r="B5" t="n">
-        <v>86830</v>
+        <v>92508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723362</v>
+        <v>723353</v>
       </c>
       <c r="R5" t="n">
-        <v>6410659</v>
+        <v>6410630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229354</v>
+        <v>129229351</v>
       </c>
       <c r="B6" t="n">
-        <v>92508</v>
+        <v>86830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723353</v>
+        <v>723362</v>
       </c>
       <c r="R6" t="n">
-        <v>6410630</v>
+        <v>6410659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229358</v>
+        <v>129229342</v>
       </c>
       <c r="B7" t="n">
-        <v>75161</v>
+        <v>86806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723311</v>
+        <v>723584</v>
       </c>
       <c r="R7" t="n">
-        <v>6410544</v>
+        <v>6410681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129229342</v>
+        <v>129229358</v>
       </c>
       <c r="B9" t="n">
-        <v>86806</v>
+        <v>75161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723584</v>
+        <v>723311</v>
       </c>
       <c r="R9" t="n">
-        <v>6410681</v>
+        <v>6410544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129229327</v>
+        <v>129229333</v>
       </c>
       <c r="B17" t="n">
-        <v>86830</v>
+        <v>91331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723204</v>
+        <v>723567</v>
       </c>
       <c r="R17" t="n">
-        <v>6410629</v>
+        <v>6410767</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129229333</v>
+        <v>129229327</v>
       </c>
       <c r="B18" t="n">
-        <v>91331</v>
+        <v>86830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723567</v>
+        <v>723204</v>
       </c>
       <c r="R18" t="n">
-        <v>6410767</v>
+        <v>6410629</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129229356</v>
+        <v>129229345</v>
       </c>
       <c r="B21" t="n">
-        <v>86968</v>
+        <v>91331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3674</v>
+        <v>2015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723325</v>
+        <v>723449</v>
       </c>
       <c r="R21" t="n">
-        <v>6410586</v>
+        <v>6410627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129229345</v>
+        <v>129229356</v>
       </c>
       <c r="B22" t="n">
-        <v>91331</v>
+        <v>86968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2015</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723449</v>
+        <v>723325</v>
       </c>
       <c r="R22" t="n">
-        <v>6410627</v>
+        <v>6410586</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129229325</v>
+        <v>129229359</v>
       </c>
       <c r="B23" t="n">
-        <v>75161</v>
+        <v>86968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723224</v>
+        <v>723306</v>
       </c>
       <c r="R23" t="n">
-        <v>6410591</v>
+        <v>6410551</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129229359</v>
+        <v>129229325</v>
       </c>
       <c r="B24" t="n">
-        <v>86968</v>
+        <v>75161</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723306</v>
+        <v>723224</v>
       </c>
       <c r="R24" t="n">
-        <v>6410551</v>
+        <v>6410591</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129229355</v>
       </c>
       <c r="B2" t="n">
-        <v>87028</v>
+        <v>87056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129229341</v>
       </c>
       <c r="B3" t="n">
-        <v>87028</v>
+        <v>87056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129229336</v>
       </c>
       <c r="B4" t="n">
-        <v>86852</v>
+        <v>86880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129229354</v>
       </c>
       <c r="B5" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129229351</v>
       </c>
       <c r="B6" t="n">
-        <v>86830</v>
+        <v>86858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229342</v>
+        <v>129229337</v>
       </c>
       <c r="B7" t="n">
-        <v>86806</v>
+        <v>86858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723584</v>
+        <v>723587</v>
       </c>
       <c r="R7" t="n">
-        <v>6410681</v>
+        <v>6410736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229337</v>
+        <v>129229342</v>
       </c>
       <c r="B8" t="n">
-        <v>86830</v>
+        <v>86834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723587</v>
+        <v>723584</v>
       </c>
       <c r="R8" t="n">
-        <v>6410736</v>
+        <v>6410681</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>129229358</v>
       </c>
       <c r="B9" t="n">
-        <v>75161</v>
+        <v>75182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129229346</v>
       </c>
       <c r="B10" t="n">
-        <v>92831</v>
+        <v>92859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129229353</v>
       </c>
       <c r="B11" t="n">
-        <v>86968</v>
+        <v>86996</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129229335</v>
       </c>
       <c r="B12" t="n">
-        <v>87028</v>
+        <v>87056</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229344</v>
+        <v>129229347</v>
       </c>
       <c r="B13" t="n">
-        <v>75161</v>
+        <v>86996</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723497</v>
+        <v>723429</v>
       </c>
       <c r="R13" t="n">
-        <v>6410619</v>
+        <v>6410682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>129229329</v>
       </c>
       <c r="B14" t="n">
-        <v>87028</v>
+        <v>87056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229347</v>
+        <v>129229348</v>
       </c>
       <c r="B15" t="n">
-        <v>86968</v>
+        <v>86858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723429</v>
+        <v>723376</v>
       </c>
       <c r="R15" t="n">
-        <v>6410682</v>
+        <v>6410721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129229348</v>
+        <v>129229344</v>
       </c>
       <c r="B16" t="n">
-        <v>86830</v>
+        <v>75182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3712</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723376</v>
+        <v>723497</v>
       </c>
       <c r="R16" t="n">
-        <v>6410721</v>
+        <v>6410619</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129229333</v>
+        <v>129229327</v>
       </c>
       <c r="B17" t="n">
-        <v>91331</v>
+        <v>86858</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2015</v>
+        <v>3712</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723567</v>
+        <v>723204</v>
       </c>
       <c r="R17" t="n">
-        <v>6410767</v>
+        <v>6410629</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129229327</v>
+        <v>129229333</v>
       </c>
       <c r="B18" t="n">
-        <v>86830</v>
+        <v>91359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723204</v>
+        <v>723567</v>
       </c>
       <c r="R18" t="n">
-        <v>6410629</v>
+        <v>6410767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>129229357</v>
       </c>
       <c r="B19" t="n">
-        <v>86830</v>
+        <v>86858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>129229331</v>
       </c>
       <c r="B20" t="n">
-        <v>92831</v>
+        <v>92859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129229345</v>
+        <v>129229356</v>
       </c>
       <c r="B21" t="n">
-        <v>91331</v>
+        <v>86996</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2015</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723449</v>
+        <v>723325</v>
       </c>
       <c r="R21" t="n">
-        <v>6410627</v>
+        <v>6410586</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129229356</v>
+        <v>129229345</v>
       </c>
       <c r="B22" t="n">
-        <v>86968</v>
+        <v>91359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3674</v>
+        <v>2015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723325</v>
+        <v>723449</v>
       </c>
       <c r="R22" t="n">
-        <v>6410586</v>
+        <v>6410627</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
         <v>129229359</v>
       </c>
       <c r="B23" t="n">
-        <v>86968</v>
+        <v>86996</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>129229325</v>
       </c>
       <c r="B24" t="n">
-        <v>75161</v>
+        <v>75182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>129229330</v>
       </c>
       <c r="B25" t="n">
-        <v>86852</v>
+        <v>86880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>129229338</v>
       </c>
       <c r="B26" t="n">
-        <v>86921</v>
+        <v>86949</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>129229343</v>
       </c>
       <c r="B27" t="n">
-        <v>86968</v>
+        <v>86996</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>129229360</v>
       </c>
       <c r="B28" t="n">
-        <v>87005</v>
+        <v>87033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 37037-2021 artfynd.xlsx
+++ b/artfynd/A 37037-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129229355</v>
+        <v>129229330</v>
       </c>
       <c r="B2" t="n">
-        <v>87056</v>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723326</v>
+        <v>723311</v>
       </c>
       <c r="R2" t="n">
-        <v>6410591</v>
+        <v>6410669</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129229341</v>
+        <v>129229336</v>
       </c>
       <c r="B3" t="n">
-        <v>87056</v>
+        <v>87193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723597</v>
+        <v>723581</v>
       </c>
       <c r="R3" t="n">
-        <v>6410706</v>
+        <v>6410745</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129229336</v>
+        <v>129229333</v>
       </c>
       <c r="B4" t="n">
-        <v>86880</v>
+        <v>91685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723581</v>
+        <v>723567</v>
       </c>
       <c r="R4" t="n">
-        <v>6410745</v>
+        <v>6410767</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129229354</v>
+        <v>129229345</v>
       </c>
       <c r="B5" t="n">
-        <v>92536</v>
+        <v>91685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>2015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723353</v>
+        <v>723449</v>
       </c>
       <c r="R5" t="n">
-        <v>6410630</v>
+        <v>6410627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129229351</v>
+        <v>129229343</v>
       </c>
       <c r="B6" t="n">
-        <v>86858</v>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723362</v>
+        <v>723553</v>
       </c>
       <c r="R6" t="n">
-        <v>6410659</v>
+        <v>6410669</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129229337</v>
+        <v>129229347</v>
       </c>
       <c r="B7" t="n">
-        <v>86858</v>
+        <v>87309</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723587</v>
+        <v>723429</v>
       </c>
       <c r="R7" t="n">
-        <v>6410736</v>
+        <v>6410682</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129229342</v>
+        <v>129229353</v>
       </c>
       <c r="B8" t="n">
-        <v>86834</v>
+        <v>87309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723584</v>
+        <v>723360</v>
       </c>
       <c r="R8" t="n">
-        <v>6410681</v>
+        <v>6410661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129229358</v>
+        <v>129229356</v>
       </c>
       <c r="B9" t="n">
-        <v>75182</v>
+        <v>87309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723311</v>
+        <v>723325</v>
       </c>
       <c r="R9" t="n">
-        <v>6410544</v>
+        <v>6410586</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129229346</v>
+        <v>129229359</v>
       </c>
       <c r="B10" t="n">
-        <v>92859</v>
+        <v>87309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4363</v>
+        <v>3674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723423</v>
+        <v>723306</v>
       </c>
       <c r="R10" t="n">
-        <v>6410659</v>
+        <v>6410551</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129229353</v>
+        <v>129229327</v>
       </c>
       <c r="B11" t="n">
-        <v>86996</v>
+        <v>87170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723360</v>
+        <v>723204</v>
       </c>
       <c r="R11" t="n">
-        <v>6410661</v>
+        <v>6410629</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129229335</v>
+        <v>129229337</v>
       </c>
       <c r="B12" t="n">
-        <v>87056</v>
+        <v>87170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723575</v>
+        <v>723587</v>
       </c>
       <c r="R12" t="n">
-        <v>6410765</v>
+        <v>6410736</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129229347</v>
+        <v>129229348</v>
       </c>
       <c r="B13" t="n">
-        <v>86996</v>
+        <v>87170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723429</v>
+        <v>723376</v>
       </c>
       <c r="R13" t="n">
-        <v>6410682</v>
+        <v>6410721</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129229329</v>
+        <v>129229351</v>
       </c>
       <c r="B14" t="n">
-        <v>87056</v>
+        <v>87170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>248947</v>
+        <v>3712</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723312</v>
+        <v>723362</v>
       </c>
       <c r="R14" t="n">
-        <v>6410667</v>
+        <v>6410659</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,14 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129229348</v>
+        <v>129229357</v>
       </c>
       <c r="B15" t="n">
-        <v>86858</v>
+        <v>87170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723376</v>
+        <v>723323</v>
       </c>
       <c r="R15" t="n">
-        <v>6410721</v>
+        <v>6410547</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129229344</v>
+        <v>129229342</v>
       </c>
       <c r="B16" t="n">
-        <v>75182</v>
+        <v>87146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>3762</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723497</v>
+        <v>723584</v>
       </c>
       <c r="R16" t="n">
-        <v>6410619</v>
+        <v>6410681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129229327</v>
+        <v>129229331</v>
       </c>
       <c r="B17" t="n">
-        <v>86858</v>
+        <v>93193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>4363</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723204</v>
+        <v>723460</v>
       </c>
       <c r="R17" t="n">
-        <v>6410629</v>
+        <v>6410693</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129229333</v>
+        <v>129229346</v>
       </c>
       <c r="B18" t="n">
-        <v>91359</v>
+        <v>93193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2015</v>
+        <v>4363</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723567</v>
+        <v>723423</v>
       </c>
       <c r="R18" t="n">
-        <v>6410767</v>
+        <v>6410659</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129229357</v>
+        <v>129229354</v>
       </c>
       <c r="B19" t="n">
-        <v>86858</v>
+        <v>92869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3712</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723323</v>
+        <v>723353</v>
       </c>
       <c r="R19" t="n">
-        <v>6410547</v>
+        <v>6410630</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129229331</v>
+        <v>129229325</v>
       </c>
       <c r="B20" t="n">
-        <v>92859</v>
+        <v>75428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4363</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723460</v>
+        <v>723224</v>
       </c>
       <c r="R20" t="n">
-        <v>6410693</v>
+        <v>6410591</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129229356</v>
+        <v>129229344</v>
       </c>
       <c r="B21" t="n">
-        <v>86996</v>
+        <v>75428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723325</v>
+        <v>723497</v>
       </c>
       <c r="R21" t="n">
-        <v>6410586</v>
+        <v>6410619</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129229345</v>
+        <v>129229358</v>
       </c>
       <c r="B22" t="n">
-        <v>91359</v>
+        <v>75428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2015</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723449</v>
+        <v>723311</v>
       </c>
       <c r="R22" t="n">
-        <v>6410627</v>
+        <v>6410544</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,45 +2712,59 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129229359</v>
+        <v>114813750</v>
       </c>
       <c r="B23" t="n">
-        <v>86996</v>
+        <v>43518</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3674</v>
+        <v>101509</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Parnassius apollo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lärbro, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723306</v>
+        <v>723645</v>
       </c>
       <c r="R23" t="n">
-        <v>6410551</v>
+        <v>6410573</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2777,12 +2791,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2797,44 +2811,48 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Patrick Gant</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Artskyddsutredning vid Lärbro 2021 (JAG0090)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129229325</v>
+        <v>129229329</v>
       </c>
       <c r="B24" t="n">
-        <v>75182</v>
+        <v>87369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>248947</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723224</v>
+        <v>723312</v>
       </c>
       <c r="R24" t="n">
-        <v>6410591</v>
+        <v>6410667</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,10 +2924,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229330</v>
+        <v>129229335</v>
       </c>
       <c r="B25" t="n">
-        <v>86880</v>
+        <v>87369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2935,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2959,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723311</v>
+        <v>723575</v>
       </c>
       <c r="R25" t="n">
-        <v>6410669</v>
+        <v>6410765</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,10 +3021,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129229338</v>
+        <v>129229341</v>
       </c>
       <c r="B26" t="n">
-        <v>86949</v>
+        <v>87369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3032,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3056,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723587</v>
+        <v>723597</v>
       </c>
       <c r="R26" t="n">
-        <v>6410736</v>
+        <v>6410706</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,32 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129229343</v>
+        <v>129229355</v>
       </c>
       <c r="B27" t="n">
-        <v>86996</v>
+        <v>87369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3674</v>
+        <v>248947</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723553</v>
+        <v>723326</v>
       </c>
       <c r="R27" t="n">
-        <v>6410669</v>
+        <v>6410591</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129229360</v>
+        <v>129229338</v>
       </c>
       <c r="B28" t="n">
-        <v>87033</v>
+        <v>87262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723286</v>
+        <v>723587</v>
       </c>
       <c r="R28" t="n">
-        <v>6410540</v>
+        <v>6410736</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3276,7 +3294,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3292,6 +3309,104 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129229360</v>
+      </c>
+      <c r="B29" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lärbro, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>723286</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6410540</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lärbro</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
